--- a/sheets/민요/검수/군밤타령 옹헤야.xlsx
+++ b/sheets/민요/검수/군밤타령 옹헤야.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4523,8 +4645,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:S14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4545,1076 +4671,955 @@
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">군밤타령 옹헤야 — 민요채보-2/군밤타령 옹헤야.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">군밤타령 옹헤야</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">왕</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="Q3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">게</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汏</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">싸</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S4" s="18"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">중</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E6" s="16"/>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">분</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汏</t>
         </is>
       </c>
-      <c r="S6" s="3"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="S6" s="17"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="E7" s="18"/>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="18"/>
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="S7" s="18"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K8" s="20"/>
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="20"/>
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="O8" s="20"/>
+      <c r="P8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="S8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="S9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="S9" s="16"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O10" s="19"/>
+      <c r="P10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="R10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S10" s="18"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">군</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="20"/>
+      <c r="P11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">분</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="S11" s="20"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I12" s="16"/>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M12" s="16"/>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O12" s="16"/>
+      <c r="P12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M13" s="3"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="R12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S12" s="16"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I13" s="18"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K13" s="18"/>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O13" s="18"/>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S13" s="18"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K14" s="20"/>
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O14" s="20"/>
+      <c r="P14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S14" s="2"/>
+      <c r="R14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S14" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:S2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="67"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/군밤타령 옹헤야.xlsx
+++ b/sheets/민요/검수/군밤타령 옹헤야.xlsx
@@ -417,7 +417,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -667,12 +667,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -739,12 +739,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="3"/>
@@ -965,13 +965,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|南</t>
+          <t xml:space="preserve">汰|–|南</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 南</t>
         </is>
       </c>
@@ -1006,13 +1006,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|潢</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1122,13 +1122,13 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|南</t>
+          <t xml:space="preserve">汰|–|南</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 南</t>
         </is>
       </c>
@@ -1163,13 +1163,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|潢</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1318,13 +1318,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|㴌</t>
+          <t xml:space="preserve">汰|–|㴌</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 㴌</t>
         </is>
       </c>
@@ -1359,13 +1359,13 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃|―|潢</t>
+          <t xml:space="preserve">黃|–|潢</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-―
+–
 潢</t>
         </is>
       </c>
@@ -1449,13 +1449,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|潢</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -1615,13 +1615,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|林</t>
+          <t xml:space="preserve">南|–|林</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 林</t>
         </is>
       </c>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1733,13 +1733,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|―|潢</t>
+          <t xml:space="preserve">林|–|潢</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―
+–
 潢</t>
         </is>
       </c>
@@ -1774,13 +1774,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|黃</t>
+          <t xml:space="preserve">汰|–|黃</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 黃</t>
         </is>
       </c>
@@ -1860,13 +1860,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1941,13 +1941,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|潢</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2661,13 +2661,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|南</t>
+          <t xml:space="preserve">潢|–|南</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 南</t>
         </is>
       </c>
@@ -2702,13 +2702,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|南</t>
+          <t xml:space="preserve">潢|–|南</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 南</t>
         </is>
       </c>
@@ -2782,13 +2782,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -2823,13 +2823,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -2864,13 +2864,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|林</t>
+          <t xml:space="preserve">南|–|林</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 林</t>
         </is>
       </c>
@@ -2944,13 +2944,13 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -2985,13 +2985,13 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|南</t>
+          <t xml:space="preserve">潢|–|南</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 南</t>
         </is>
       </c>
@@ -3026,13 +3026,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|林</t>
+          <t xml:space="preserve">潢|–|林</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 林</t>
         </is>
       </c>
@@ -3106,13 +3106,13 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -3225,7 +3225,7 @@
       <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 南</t>
         </is>
       </c>
@@ -3285,7 +3285,7 @@
       <c r="B4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 南</t>
         </is>
       </c>
@@ -3310,7 +3310,7 @@
       <c r="H4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 林</t>
         </is>
       </c>
@@ -3322,7 +3322,7 @@
       <c r="J4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 南</t>
         </is>
       </c>
@@ -3366,7 +3366,7 @@
       <c r="G5" s="9"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3374,7 +3374,7 @@
       <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -3397,7 +3397,7 @@
       <c r="B6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3452,7 +3452,7 @@
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -3477,7 +3477,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―
+–
 潢</t>
         </is>
       </c>
@@ -3510,7 +3510,7 @@
       <c r="B8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 林</t>
         </is>
       </c>
@@ -3535,7 +3535,7 @@
       <c r="H8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 黃</t>
         </is>
       </c>
@@ -3547,7 +3547,7 @@
       <c r="J8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 南</t>
         </is>
       </c>
@@ -3594,7 +3594,7 @@
       <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -3617,7 +3617,7 @@
       <c r="B10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3676,7 +3676,7 @@
       <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 南</t>
         </is>
       </c>
@@ -3701,7 +3701,7 @@
       <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       <c r="B12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 林</t>
         </is>
       </c>
@@ -3788,7 +3788,7 @@
       <c r="O12" s="9"/>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -3823,7 +3823,7 @@
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="J13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 㴌</t>
         </is>
       </c>
@@ -3863,7 +3863,7 @@
       <c r="B14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -3887,7 +3887,7 @@
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3895,7 +3895,7 @@
       <c r="J14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-―
+–
 潢</t>
         </is>
       </c>
@@ -3910,7 +3910,7 @@
       <c r="O14" s="10"/>
       <c r="P14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="13"/>
@@ -3983,7 +3983,7 @@
       <c r="J16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>

--- a/sheets/민요/검수/군밤타령 옹헤야.xlsx
+++ b/sheets/민요/검수/군밤타령 옹헤야.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3197,907 +3238,907 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">군밤타령 옹헤야</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에헤</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="F3" s="17"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="F3" s="21"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼싸</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="L3" s="21"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R3" s="17"/>
-      <c r="S3" s="8"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 南</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에헤</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 黃</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">헤야</t>
         </is>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="F4" s="21"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 林</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">좋네</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 南</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="9"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="F5" s="21"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="25"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 潢</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이분다</t>
         </is>
       </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="9"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 南</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">해야</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 黃</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">헤야</t>
         </is>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="F6" s="21"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
 潢</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하좋아</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="10"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="26"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 南</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어절</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">모두</t>
         </is>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="F7" s="21"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –
 潢</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">군밤</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="8"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 林</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">씨구</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">같이</t>
         </is>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="F8" s="21"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 黃</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이요</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 南</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="9"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="F9" s="21"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 潢</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이분다</t>
         </is>
       </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="9"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 南</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">해야</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">헤야</t>
         </is>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="F10" s="21"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에헤라</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="K10" s="26"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="10"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 南</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">잘도</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">즐거</t>
         </is>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="F11" s="21"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">생율</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
       </c>
-      <c r="L11" s="17"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="L11" s="21"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="8"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 林</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">한다</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">웁게</t>
         </is>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="F12" s="21"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 南
 林</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">밤이로</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">평</t>
         </is>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="L12" s="21"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="9"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="F13" s="21"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 潢</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구나</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 㴌</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="L13" s="21"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="9"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 南</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">헤야</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">헤야</t>
         </is>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="F14" s="21"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="I14" s="26"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 –
 潢</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다에</t>
         </is>
       </c>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="18" t="inlineStr">
+      <c r="L14" s="21"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="10"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="26"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">노래</t>
         </is>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L15" s="17"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="L15" s="21"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="8"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하세</t>
         </is>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="F16" s="21"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 潢</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">얼싸</t>
         </is>
       </c>
-      <c r="L16" s="17"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="18" t="inlineStr">
+      <c r="L16" s="21"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢
 汰</t>
         </is>
       </c>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="9"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="F17" s="21"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">돈바람</t>
         </is>
       </c>
-      <c r="L17" s="17"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="L17" s="21"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="9"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="C18" s="27"/>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">헤야</t>
         </is>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="F18" s="21"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="K18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">분다</t>
         </is>
       </c>
-      <c r="L18" s="17"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="L18" s="21"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="10"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/군밤타령 옹헤야.xlsx
+++ b/sheets/민요/검수/군밤타령 옹헤야.xlsx
@@ -3213,30 +3213,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
       <c r="R3" s="21"/>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
       <c r="R6" s="21"/>
       <c r="S6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
       <c r="R7" s="21"/>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4002,7 +4002,7 @@
       <c r="R15" s="21"/>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -4048,7 +4048,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -4092,7 +4092,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/군밤타령 옹헤야.xlsx
+++ b/sheets/민요/검수/군밤타령 옹헤야.xlsx
@@ -3188,12 +3188,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I67" s="3"/>
@@ -4096,7 +4096,7 @@
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" s="27"/>
